--- a/CYP2B6/CYP2B6_allele_definition_table.xlsx
+++ b/CYP2B6/CYP2B6_allele_definition_table.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2B6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2B6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11010"/>
   </bookViews>
   <sheets>
     <sheet name="Alleles" sheetId="1" r:id="rId1"/>
     <sheet name="Notes" sheetId="2" r:id="rId2"/>
     <sheet name="Change log" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -999,7 +999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1017,6 +1017,14 @@
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1048,10 +1056,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1078,8 +1087,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1093,6 +1104,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1" descr="Schematic representation of the CYP2B6*29 and *30 fusion allele... |  Download Scientific Diagram"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="54368700" y="9420225"/>
+          <a:ext cx="5981700" cy="1495425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2576,7 +2647,7 @@
       <c r="AX35" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AY35" t="s">
+      <c r="AY35" s="10" t="s">
         <v>323</v>
       </c>
     </row>
@@ -2827,7 +2898,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="AY35" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
